--- a/geopackage/UoM/unitofmeasure_UCUM_QUDT_SI_Agreed.xlsx
+++ b/geopackage/UoM/unitofmeasure_UCUM_QUDT_SI_Agreed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kathi\Dropbox\cove\SoilWise\WP2\GPkg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E82CE4EF-9008-46E9-AB58-0CC73FAD5544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADDFBD0B-E92D-4B28-9E14-D53D2255E455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="144">
   <si>
     <t>id</t>
   </si>
@@ -471,9 +471,6 @@
   </si>
   <si>
     <t>NanoMOL-PER-GM-HR</t>
-  </si>
-  <si>
-    <t>Mole per Second Kilogram</t>
   </si>
   <si>
     <t>mmol/kg</t>
@@ -1822,13 +1819,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E12" s="20" t="s">
         <v>33</v>
@@ -2071,7 +2068,7 @@
         <v>141</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H20" s="5">
         <v>0</v>
@@ -2345,13 +2342,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>87</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>88</v>
@@ -2438,12 +2435,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dbd51d17-bbc6-4561-bad9-1ecb28b6579b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="714bb49a-ac39-48ce-83d9-0378084804bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2676,20 +2675,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dbd51d17-bbc6-4561-bad9-1ecb28b6579b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="714bb49a-ac39-48ce-83d9-0378084804bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBB0B41C-4853-4EF7-AA0A-1F0BB91BF59E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E82A10EB-C398-447D-B82D-F30561A2B763}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dbd51d17-bbc6-4561-bad9-1ecb28b6579b"/>
+    <ds:schemaRef ds:uri="714bb49a-ac39-48ce-83d9-0378084804bd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2714,12 +2714,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E82A10EB-C398-447D-B82D-F30561A2B763}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBB0B41C-4853-4EF7-AA0A-1F0BB91BF59E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dbd51d17-bbc6-4561-bad9-1ecb28b6579b"/>
-    <ds:schemaRef ds:uri="714bb49a-ac39-48ce-83d9-0378084804bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>